--- a/excel/intake_substation_c.xlsx
+++ b/excel/intake_substation_c.xlsx
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1011,353 +1011,332 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>B-180</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>INCOMER BUS 1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2500A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>31.5KA</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>7SJ85
+P1J2253039
+R-4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2500:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TX "B" 40/66MVA 115/34.5KV</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PT BUS 1</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>POTENTIAL TRANSFORMER BUS 1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>34.5KV:120V</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.5A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TX AUX 1</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TX AUX 1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>630A</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>31.5KA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7SJ85
+P1J1617696
+R-10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>600:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TX AUX 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>B-105</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>CTO. 13C</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1250A</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>31.5KA</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7SJ85
+P1J2253039
+R-3</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>CTO. 13C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>B-205</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>CTO. C</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1250A</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>31.5KA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7SJ85
+P1J2253039
+R-2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>CTO. C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>B-305</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>CTO. 15B</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1200A</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1250A</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>CTO. 15B</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>B-205</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CTO. C</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>1200A</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>31.5KA</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7SJ85
-P1J2253039
-R-2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>CTO. C</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>B-105</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CTO. 13C</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>1200A</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>31.5KA</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7SJ85
-P1J2253039
-R-3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>CTO. 13C</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>incomer</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>B-180</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>INCOMER BUS 1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2500A</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>31.5KA</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7SJ85
-P1J2253039
-R-4</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2500:5A (3)</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2500:5A (3)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>TX "B" 40/66MVA 115/34.5KV</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TX AUX 1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TX AUX 1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>1200A</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>31.5KA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>7SJ85
-P1J1617696
-R-10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>600:5A (3)</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>600:5A (3)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>TX AUX 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>PT BUS 1</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>POTENTIAL
-TRANSFORMER BUS 1</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>34.5KV:120V</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1366,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>38KV</t>
+          <t>40.5KV</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1409,17 +1388,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2500:5A (3)</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2500:5A (3)</t>
+          <t>2500:5/5A (3)</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>5P20</t>
+          <t>5P20/5P20</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1442,20 +1416,9 @@
           <t>single</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PT BUS 2</t>
-        </is>
-      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>POTENTIAL
-TRANSFORMER BUS 2</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>34.5KV:120V</t>
+          <t>RISER</t>
         </is>
       </c>
     </row>
@@ -1475,322 +1438,372 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>B-405</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CTO. 15A</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1250A</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>31.5KA</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7SJ85
+P1J2253039
+R-7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>CTO. 15A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>B-505</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CTO. 19C</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1250A</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>31.5KA</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>7SJ85
+P1J2253039
+R-6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>CTO. 19C</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>B-605</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CTO. 14C</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1250A</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>31.5KA</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>7SJ85
+P1J2253039
+R-5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>CTO. 14C</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>TX AUX 2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>TX AUX 2</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1200A</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>630A</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>7SJ85
 P1J1617696
 R-11</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>600:5A (3)</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>600:5A (3)</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>600:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>TX AUX 2</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>incomer</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PT BUS 2</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>POTENTIAL TRANSFORMER BUS 2</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>34.5KV:120V</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.5A</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
         <is>
           <t>B-280</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>INCOMER BUS 2</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>40.5KV</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>2500A</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-8</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2500:5A (3)</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2500:5A (3)</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2500:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>5P20/5P20</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>TX "A" 40/66MVA 115/34.5KV</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="inlineStr">
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>B-405</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CTO. 15A</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1200A</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>31.5KA</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>7SJ85
-P1J2253039
-R-7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>CTO. 15A</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" t="inlineStr">
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>SPARE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>single</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>B-505</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CTO. 19C</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>1200A</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>31.5KA</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>7SJ85
-P1J2253039
-R-6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>CTO. 19C</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>single</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>B-605</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CTO. 14C</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>38KV</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1200A</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>31.5KA</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>7SJ85
-P1J2253039
-R-5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>1200:5A (3)</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>5P20</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>CTO. 14C</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>SPARE</t>
         </is>
       </c>
     </row>

--- a/excel/intake_substation_c.xlsx
+++ b/excel/intake_substation_c.xlsx
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -966,30 +966,35 @@
       </c>
       <c r="K1" s="18" t="inlineStr">
         <is>
+          <t>ct_differential</t>
+        </is>
+      </c>
+      <c r="L1" s="18" t="inlineStr">
+        <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1046,12 +1051,17 @@
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2500:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>TX "B" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1081,12 +1091,12 @@
           <t>POTENTIAL TRANSFORMER BUS 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1143,12 +1153,17 @@
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>600:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>TX AUX 1</t>
         </is>
@@ -1205,12 +1220,17 @@
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>CTO. 13C</t>
         </is>
@@ -1267,12 +1287,17 @@
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>CTO. C</t>
         </is>
@@ -1329,12 +1354,17 @@
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>CTO. 15B</t>
         </is>
@@ -1391,12 +1421,17 @@
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2500:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>BUS 2</t>
         </is>
@@ -1473,12 +1508,17 @@
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>CTO. 15A</t>
         </is>
@@ -1535,12 +1575,17 @@
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>CTO. 19C</t>
         </is>
@@ -1597,12 +1642,17 @@
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1200:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>CTO. 14C</t>
         </is>
@@ -1659,12 +1709,17 @@
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>600:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>TX AUX 2</t>
         </is>
@@ -1694,12 +1749,12 @@
           <t>POTENTIAL TRANSFORMER BUS 2</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1756,12 +1811,17 @@
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>2500:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>TX "A" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1826,7 +1886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1975,89 +2035,97 @@
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="7" t="n"/>
-    </row>
     <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
       <c r="B21" s="7" t="n"/>
     </row>
     <row r="22">
@@ -2079,6 +2147,10 @@
     <row r="26">
       <c r="A26" s="4" t="n"/>
       <c r="B26" s="7" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_substation_c.xlsx
+++ b/excel/intake_substation_c.xlsx
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -961,40 +961,45 @@
       </c>
       <c r="J1" s="18" t="inlineStr">
         <is>
+          <t>bus_differential</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
           <t>ct_protection</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>ct_differential</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1046,22 +1051,22 @@
 R-4</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>TX "B" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1091,12 +1096,12 @@
           <t>POTENTIAL TRANSFORMER BUS 1</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1148,22 +1153,22 @@
 R-10</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>TX AUX 1</t>
         </is>
@@ -1215,22 +1220,22 @@
 R-3</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>CTO. 13C</t>
         </is>
@@ -1282,22 +1287,22 @@
 R-2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>CTO. C</t>
         </is>
@@ -1349,22 +1354,22 @@
 R-1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>CTO. 15B</t>
         </is>
@@ -1418,20 +1423,25 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>87B</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>BUS 2</t>
         </is>
@@ -1503,22 +1513,22 @@
 R-7</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>CTO. 15A</t>
         </is>
@@ -1570,22 +1580,22 @@
 R-6</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>CTO. 19C</t>
         </is>
@@ -1637,22 +1647,22 @@
 R-5</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>CTO. 14C</t>
         </is>
@@ -1704,22 +1714,22 @@
 R-11</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>TX AUX 2</t>
         </is>
@@ -1749,12 +1759,12 @@
           <t>POTENTIAL TRANSFORMER BUS 2</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1806,22 +1816,22 @@
 R-8</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>TX "A" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1886,7 +1896,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2023,113 +2033,121 @@
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>ct_protection</t>
+          <t>bus_differential</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
+          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>ct_differential</t>
+          <t>ct_protection</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
+          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="7" t="n"/>
-    </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="7" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
       <c r="B22" s="7" t="n"/>
     </row>
     <row r="23">
@@ -2151,6 +2169,10 @@
     <row r="27">
       <c r="A27" s="4" t="n"/>
       <c r="B27" s="7" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_substation_c.xlsx
+++ b/excel/intake_substation_c.xlsx
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -961,45 +961,50 @@
       </c>
       <c r="J1" s="18" t="inlineStr">
         <is>
+          <t>relay_fuse</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
           <t>bus_differential</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>ct_protection</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_differential</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="S1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1051,22 +1056,22 @@
 R-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>TX "B" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1096,12 +1101,12 @@
           <t>POTENTIAL TRANSFORMER BUS 1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1153,22 +1158,22 @@
 R-10</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>TX AUX 1</t>
         </is>
@@ -1220,22 +1225,22 @@
 R-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>CTO. 13C</t>
         </is>
@@ -1287,22 +1292,22 @@
 R-2</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>CTO. C</t>
         </is>
@@ -1354,22 +1359,22 @@
 R-1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>CTO. 15B</t>
         </is>
@@ -1421,27 +1426,27 @@
 R-9</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>87B</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>BUS 2</t>
         </is>
@@ -1513,22 +1518,22 @@
 R-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>CTO. 15A</t>
         </is>
@@ -1580,22 +1585,22 @@
 R-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>CTO. 19C</t>
         </is>
@@ -1647,22 +1652,22 @@
 R-5</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>CTO. 14C</t>
         </is>
@@ -1714,22 +1719,22 @@
 R-11</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>TX AUX 2</t>
         </is>
@@ -1759,12 +1764,12 @@
           <t>POTENTIAL TRANSFORMER BUS 2</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1816,22 +1821,22 @@
 R-8</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>TX "A" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1896,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2033,125 +2038,133 @@
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>bus_differential</t>
+          <t>relay_fuse</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
+          <t>Optional. Fuse on this relay's supply where it drops off the reference run, e.g. 6A. Leave blank to take the house default.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>ct_protection</t>
+          <t>bus_differential</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
+          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ct_differential</t>
+          <t>ct_protection</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
+          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="7" t="n"/>
-    </row>
     <row r="22">
-      <c r="A22" s="25" t="inlineStr">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
       <c r="B23" s="7" t="n"/>
     </row>
     <row r="24">
@@ -2173,6 +2186,10 @@
     <row r="28">
       <c r="A28" s="4" t="n"/>
       <c r="B28" s="7" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_substation_c.xlsx
+++ b/excel/intake_substation_c.xlsx
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S17"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -941,70 +941,75 @@
       </c>
       <c r="F1" s="18" t="inlineStr">
         <is>
+          <t>tie</t>
+        </is>
+      </c>
+      <c r="G1" s="18" t="inlineStr">
+        <is>
           <t>voltage</t>
         </is>
       </c>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="H1" s="18" t="inlineStr">
         <is>
           <t>amp_rating</t>
         </is>
       </c>
-      <c r="H1" s="18" t="inlineStr">
+      <c r="I1" s="18" t="inlineStr">
         <is>
           <t>ka_rating</t>
         </is>
       </c>
-      <c r="I1" s="18" t="inlineStr">
+      <c r="J1" s="18" t="inlineStr">
         <is>
           <t>relay</t>
         </is>
       </c>
-      <c r="J1" s="18" t="inlineStr">
+      <c r="K1" s="18" t="inlineStr">
         <is>
           <t>relay_fuse</t>
         </is>
       </c>
-      <c r="K1" s="18" t="inlineStr">
+      <c r="L1" s="18" t="inlineStr">
         <is>
           <t>bus_differential</t>
         </is>
       </c>
-      <c r="L1" s="18" t="inlineStr">
+      <c r="M1" s="18" t="inlineStr">
         <is>
           <t>ct_protection</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_differential</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="S1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="S1" s="18" t="inlineStr">
+      <c r="T1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1034,44 +1039,44 @@
           <t>INCOMER BUS 1</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2500A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-4</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>TX "B" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1101,12 +1106,12 @@
           <t>POTENTIAL TRANSFORMER BUS 1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1136,44 +1141,44 @@
           <t>TX AUX 1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>630A</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>7SJ85
 P1J1617696
 R-10</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>TX AUX 1</t>
         </is>
@@ -1203,44 +1208,44 @@
           <t>CTO. 13C</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>1250A</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-3</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>CTO. 13C</t>
         </is>
@@ -1270,44 +1275,44 @@
           <t>CTO. C</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>1250A</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-2</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>CTO. C</t>
         </is>
@@ -1337,44 +1342,44 @@
           <t>CTO. 15B</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>1250A</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-1</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>CTO. 15B</t>
         </is>
@@ -1406,49 +1411,44 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>N.C.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>2500A</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>7SJ85
 P1J1120691
 R-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>87B</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2500:5/5A (3)</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>BUS 2</t>
         </is>
       </c>
     </row>
@@ -1496,44 +1496,44 @@
           <t>CTO. 15A</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>1250A</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-7</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>CTO. 15A</t>
         </is>
@@ -1563,44 +1563,44 @@
           <t>CTO. 19C</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>1250A</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-6</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>CTO. 19C</t>
         </is>
@@ -1630,44 +1630,44 @@
           <t>CTO. 14C</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>1250A</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-5</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>CTO. 14C</t>
         </is>
@@ -1697,44 +1697,44 @@
           <t>TX AUX 2</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>630A</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>7SJ85
 P1J1617696
 R-11</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>TX AUX 2</t>
         </is>
@@ -1764,12 +1764,12 @@
           <t>POTENTIAL TRANSFORMER BUS 2</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1799,44 +1799,44 @@
           <t>INCOMER BUS 2</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>40.5KV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2500A</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>31.5KA</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>7SJ85
 P1J2253039
 R-8</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>TX "A" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1901,7 +1901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1990,185 +1990,193 @@
     <row r="8">
       <c r="A8" s="24" t="inlineStr">
         <is>
-          <t>voltage</t>
+          <t>tie</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Breaker rated maximum voltage, e.g. 15kV.</t>
+          <t>Fill on the bus tie, with its normal position, e.g. N.C. The breaker is then drawn lying IN the bus instead of hanging off it, and the bus breaks there -- which is what makes the lineup two buses instead of one.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="24" t="inlineStr">
         <is>
-          <t>amp_rating</t>
+          <t>voltage</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Breaker continuous current. BLANK MEANS NO BREAKER -- that is how a deck holds only a bus PT.</t>
+          <t>Breaker rated maximum voltage, e.g. 15kV.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="24" t="inlineStr">
         <is>
-          <t>ka_rating</t>
+          <t>amp_rating</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Breaker interrupting rating.</t>
+          <t>Breaker continuous current. BLANK MEANS NO BREAKER -- that is how a deck holds only a bus PT.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="24" t="inlineStr">
         <is>
-          <t>relay</t>
+          <t>ka_rating</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Protection relay model. Drawn as a labelled box beside the breaker.</t>
+          <t>Breaker interrupting rating.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="24" t="inlineStr">
         <is>
-          <t>relay_fuse</t>
+          <t>relay</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Optional. Fuse on this relay's supply where it drops off the reference run, e.g. 6A. Leave blank to take the house default.</t>
+          <t>Protection relay model. Drawn as a labelled box beside the breaker.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="24" t="inlineStr">
         <is>
-          <t>bus_differential</t>
+          <t>relay_fuse</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
+          <t>Optional. Fuse on this relay's supply where it drops off the reference run, e.g. 6A. Leave blank to take the house default.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>ct_protection</t>
+          <t>bus_differential</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
+          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_differential</t>
+          <t>ct_protection</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
+          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="7" t="n"/>
-    </row>
     <row r="23">
-      <c r="A23" s="25" t="inlineStr">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="7" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B23" s="7" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="n"/>
       <c r="B24" s="7" t="n"/>
     </row>
     <row r="25">
@@ -2190,6 +2198,10 @@
     <row r="29">
       <c r="A29" s="4" t="n"/>
       <c r="B29" s="7" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/excel/intake_substation_c.xlsx
+++ b/excel/intake_substation_c.xlsx
@@ -1106,6 +1106,18 @@
           <t>POTENTIAL TRANSFORMER BUS 1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>7SS85
+P1E1122954
+R-12</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>87B1</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
@@ -1436,11 +1448,6 @@
 R-9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>87B</t>
-        </is>
-      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
@@ -1762,6 +1769,18 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>POTENTIAL TRANSFORMER BUS 2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>7SS85
+P1E1122954
+R-13</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>87B2</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">

--- a/excel/intake_substation_c.xlsx
+++ b/excel/intake_substation_c.xlsx
@@ -893,7 +893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -971,45 +971,50 @@
       </c>
       <c r="L1" s="18" t="inlineStr">
         <is>
+          <t>merging_unit</t>
+        </is>
+      </c>
+      <c r="M1" s="18" t="inlineStr">
+        <is>
           <t>bus_differential</t>
         </is>
       </c>
-      <c r="M1" s="18" t="inlineStr">
+      <c r="N1" s="18" t="inlineStr">
         <is>
           <t>ct_protection</t>
         </is>
       </c>
-      <c r="N1" s="18" t="inlineStr">
+      <c r="O1" s="18" t="inlineStr">
         <is>
           <t>ct_differential</t>
         </is>
       </c>
-      <c r="O1" s="18" t="inlineStr">
+      <c r="P1" s="18" t="inlineStr">
         <is>
           <t>ct_metering</t>
         </is>
       </c>
-      <c r="P1" s="18" t="inlineStr">
+      <c r="Q1" s="18" t="inlineStr">
         <is>
           <t>ct_ground</t>
         </is>
       </c>
-      <c r="Q1" s="18" t="inlineStr">
+      <c r="R1" s="18" t="inlineStr">
         <is>
           <t>ct_class</t>
         </is>
       </c>
-      <c r="R1" s="18" t="inlineStr">
+      <c r="S1" s="18" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="S1" s="18" t="inlineStr">
+      <c r="T1" s="18" t="inlineStr">
         <is>
           <t>pt_primary_fuse</t>
         </is>
       </c>
-      <c r="T1" s="18" t="inlineStr">
+      <c r="U1" s="18" t="inlineStr">
         <is>
           <t>destination</t>
         </is>
@@ -1061,22 +1066,22 @@
 R-4</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>TX "B" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1113,17 +1118,17 @@
 R-12</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>87B1</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1175,22 +1180,22 @@
 R-10</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>TX AUX 1</t>
         </is>
@@ -1242,22 +1247,22 @@
 R-3</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>CTO. 13C</t>
         </is>
@@ -1309,22 +1314,22 @@
 R-2</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>CTO. C</t>
         </is>
@@ -1376,22 +1381,22 @@
 R-1</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>CTO. 15B</t>
         </is>
@@ -1448,12 +1453,24 @@
 R-9</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>6MU85
+P1M311366
+MU-1</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2500:5/5A (3)</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
@@ -1525,22 +1542,22 @@
 R-7</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>CTO. 15A</t>
         </is>
@@ -1592,22 +1609,22 @@
 R-6</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>CTO. 19C</t>
         </is>
@@ -1659,22 +1676,22 @@
 R-5</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>1200:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>CTO. 14C</t>
         </is>
@@ -1726,22 +1743,22 @@
 R-11</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>600:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>TX AUX 2</t>
         </is>
@@ -1778,17 +1795,17 @@
 R-13</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>87B2</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>34.5KV:120V</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>0.5A</t>
         </is>
@@ -1840,22 +1857,22 @@
 R-8</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>2500:5/5A (3)</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>5P20/5P20</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>TX "A" 40/66MVA 115/34.5KV</t>
         </is>
@@ -1920,7 +1937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2081,125 +2098,133 @@
     <row r="14">
       <c r="A14" s="24" t="inlineStr">
         <is>
-          <t>bus_differential</t>
+          <t>merging_unit</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
+          <t>Merging unit model, e.g. 6MU85. Drawn as a second box beside the relay, fed by its own CT and by one bus's voltage reference. Tie cubicles only.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="24" t="inlineStr">
         <is>
-          <t>ct_protection</t>
+          <t>bus_differential</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
+          <t>Fill on the ONE cubicle whose relay is the bus differential relay, e.g. 87B. Every ct_differential in the lineup is wired to it. Leave blank everywhere else -- and if no cubicle states it, the differential CTs are drawn with no run, because there is nothing for them to run to.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="24" t="inlineStr">
         <is>
-          <t>ct_differential</t>
+          <t>ct_protection</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
+          <t>Protection CT ratio and quantity, e.g. 400:5A (3).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="24" t="inlineStr">
         <is>
-          <t>ct_metering</t>
+          <t>ct_differential</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
+          <t>Ratio of the CT feeding bus differential, e.g. 1200:5A (3). A dual-core CT (1200/5/5A) is one device in the panel schedule and two symbols here, because the two cores feed different circuits. On a tie this is the far bus's differential.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="24" t="inlineStr">
         <is>
-          <t>ct_ground</t>
+          <t>ct_metering</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
+          <t>Metering CT. Fill this ONLY if the cubicle really has a second CT set -- leaving it blank is what keeps one-CT feeders to one CT.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="24" t="inlineStr">
         <is>
-          <t>ct_class</t>
+          <t>ct_ground</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
+          <t>Separate ground-fault CT, e.g. 50:5A. Motor feeders.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="24" t="inlineStr">
         <is>
-          <t>pt</t>
+          <t>ct_class</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
+          <t>Optional. Accuracy class stamped on every CT in this cubicle, e.g. 5P20. Leave blank to take the house default for each CT's job (5P20 protection, 0.3B1.8 metering, GND CT).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="24" t="inlineStr">
         <is>
-          <t>pt_primary_fuse</t>
+          <t>pt</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+          <t>Bus PT ratio, e.g. 14,400:120V. The cubicle that states this gets the PT branch, and its secondary feeds every relay in the lineup.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="24" t="inlineStr">
         <is>
+          <t>pt_primary_fuse</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>PT primary fuse, e.g. CLF 0.5E. The secondary fuse belongs on the three-line diagram, not here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
           <t>destination</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Source or load text printed at the cubicle entry / exit. A future feeder is a normal feeder whose destination says so.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="7" t="n"/>
-    </row>
     <row r="24">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>A device is drawn if and only if its cell has a value.</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="n"/>
       <c r="B25" s="7" t="n"/>
     </row>
     <row r="26">
@@ -2221,6 +2246,10 @@
     <row r="30">
       <c r="A30" s="4" t="n"/>
       <c r="B30" s="7" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="7" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
